--- a/DDD_Route_Architecture_Full_Model.xlsx
+++ b/DDD_Route_Architecture_Full_Model.xlsx
@@ -1,40 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DTOs_Trowmodels" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interfaces" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_Necessarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_Distance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_Graph" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_TSP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_VRP" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services_Parallel" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Complexity_Gargalos" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark_Teorico" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencias" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap_1000plus" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entities_Full_Model" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entities" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity_Relationships" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invariants_And_Rules" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WebSocket_Push" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Display" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entities_Additional_Suggested" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL_Enums" sheetId="21" state="visible" r:id="rId21"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
+  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
+  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-03-03T00:54:40Z</dcterms:created>
+  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-03-03T10:11:46Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="2">
@@ -160,7 +140,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -443,7 +423,42 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DTOs_Trowmodels" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interfaces" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_Necessarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_Distance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_Graph" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_TSP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_VRP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services_Parallel" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Complexity_Gargalos" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark_Teorico" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencias" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap_1000plus" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entities_Full_Model" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entities" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity_Relationships" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invariants_And_Rules" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WebSocket_Push" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Display" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entities_Additional_Suggested" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL_Enums" sheetId="21" state="visible" r:id="rId21"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -617,7 +632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -795,7 +810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -903,7 +918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1033,13 +1048,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2523,18 +2538,977 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Identity aggregate root</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>IDX_email (unique)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Unique login identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>password_hash</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>BCrypt password hash</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Display name</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>vehicle_id</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>JWT claim for tracking payload authorization</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>user_role_enum</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>IDX_role</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>USER or ADMIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>remember_me_token</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>VARCHAR(512)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IDX_remember_me</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Hashed remember-me token</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>remember_me_expires_at</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Remember-me expiration</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Soft delete / account disable flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Audit timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Audit timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Opaque refresh token record</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>app_user(id)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>IDX_refresh_token_user</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Session owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>token_hash</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Hashed opaque refresh token</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>IDX_refresh_token_session</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Groups tokens by device/session</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>access_jti</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>IDX_refresh_token_access_jti</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Access token jti for immediate blocklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>access_expires_at</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>TTL source for revoked access tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>expires_at</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>IDX_refresh_token_expires</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Refresh token expiration</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>revoked</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Session revocation flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Audit timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>password_reset_token</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>One-time password reset token</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>password_reset_token</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>app_user(id)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>IDX_password_reset_token_user</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Token owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>password_reset_token</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>token_hash</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Hashed reset token</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>password_reset_token</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>expires_at</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>IDX_password_reset_token_expires</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Reset token expiration</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>password_reset_token</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Marks token consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>password_reset_token</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TIMESTAMP WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Audit timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>OptimizationEngine</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RouteOptimization</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>route_segment</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>traffic_level</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Derived from active incidents for map rendering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2916,18 +3890,129 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Users and roles</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>id (PK)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Stores login identity, role and remember-me state</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Session store</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>id (PK), user_id (FK), session_id</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Opaque refresh tokens with jti metadata for blocklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AppUser</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>password_reset_token</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Password recovery</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>id (PK), user_id (FK)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>One-time reset tokens with TTL and used_at</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3444,12 +4529,96 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>refresh_token</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fk_refresh_token_user</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Refresh sessions belong to a user</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>password_reset_token</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fk_password_reset_token_user</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reset tokens belong to a user</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3731,13 +4900,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4179,12 +5348,39 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UserRole</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>USER, ADMIN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>user_role_enum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>app_user.role</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Authorization role for public users and administrators</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4340,7 +5536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4478,7 +5674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4586,7 +5782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6422,13 +7618,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6789,12 +7985,34 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>user_role_enum</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>USER, ADMIN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>V006 / V009</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7112,7 +8330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7187,7 +8405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7316,7 +8534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7445,7 +8663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7574,7 +8792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7649,7 +8867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
